--- a/R_analysis/output/tables/Tabela_Raca_Cor_anual.xlsx
+++ b/R_analysis/output/tables/Tabela_Raca_Cor_anual.xlsx
@@ -382,7 +382,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C2">
@@ -390,7 +390,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -400,7 +400,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C3">
@@ -408,7 +408,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C4">
@@ -426,7 +426,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C5">
@@ -444,7 +444,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C6">
@@ -462,7 +462,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C7">
@@ -480,7 +480,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C8">
@@ -498,7 +498,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C9">
@@ -516,7 +516,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C10">
@@ -534,7 +534,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C11">
@@ -552,7 +552,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C12">
@@ -570,7 +570,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C13">
@@ -588,7 +588,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C14">
@@ -606,7 +606,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C15">
@@ -624,7 +624,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C16">
@@ -642,7 +642,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C17">
@@ -660,7 +660,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C18">
@@ -678,7 +678,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -688,15 +688,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C19">
-        <v>1269</v>
+        <v>495</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -706,15 +706,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C20">
-        <v>1229</v>
+        <v>730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -724,15 +724,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C21">
-        <v>1364</v>
+        <v>723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -742,15 +742,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C22">
-        <v>1656</v>
+        <v>758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -760,15 +760,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C23">
-        <v>2113</v>
+        <v>1123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -778,15 +778,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C24">
-        <v>2597</v>
+        <v>1295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -796,15 +796,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C25">
-        <v>3355</v>
+        <v>1461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -814,15 +814,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C26">
-        <v>3808</v>
+        <v>1696</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -832,15 +832,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C27">
-        <v>4849</v>
+        <v>1947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -850,15 +850,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C28">
-        <v>5282</v>
+        <v>2155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -868,15 +868,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C29">
-        <v>6301</v>
+        <v>2366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -886,15 +886,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C30">
-        <v>6248</v>
+        <v>2418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -904,15 +904,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C31">
-        <v>6037</v>
+        <v>2339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -922,15 +922,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C32">
-        <v>5212</v>
+        <v>2021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -940,15 +940,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C33">
-        <v>6156</v>
+        <v>2344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C34">
-        <v>6386</v>
+        <v>2275</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -976,15 +976,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C35">
-        <v>6137</v>
+        <v>2206</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -994,15 +994,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C36">
-        <v>1032</v>
+        <v>26</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1012,15 +1012,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C37">
-        <v>728</v>
+        <v>59</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1030,15 +1030,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C38">
-        <v>704</v>
+        <v>62</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1048,15 +1048,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C39">
-        <v>899</v>
+        <v>45</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1066,15 +1066,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C40">
-        <v>1122</v>
+        <v>45</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1084,15 +1084,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C41">
-        <v>1240</v>
+        <v>37</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1102,15 +1102,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C42">
-        <v>1539</v>
+        <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1120,15 +1120,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C43">
-        <v>1547</v>
+        <v>45</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C44">
-        <v>2048</v>
+        <v>56</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1156,15 +1156,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C45">
-        <v>1978</v>
+        <v>85</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1174,15 +1174,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C46">
-        <v>2161</v>
+        <v>78</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1192,15 +1192,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C47">
-        <v>2433</v>
+        <v>72</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1210,15 +1210,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C48">
-        <v>2182</v>
+        <v>68</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1228,15 +1228,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C49">
-        <v>2169</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1246,15 +1246,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C50">
-        <v>2386</v>
+        <v>63</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1264,15 +1264,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C51">
-        <v>2225</v>
+        <v>72</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1282,15 +1282,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C52">
-        <v>1553</v>
+        <v>80</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1300,15 +1300,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>2550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1318,15 +1318,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C54">
-        <v>59</v>
+        <v>2987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1336,15 +1336,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C55">
-        <v>62</v>
+        <v>3234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1354,15 +1354,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C56">
-        <v>45</v>
+        <v>3630</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1372,15 +1372,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C57">
-        <v>45</v>
+        <v>5151</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1390,15 +1390,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C58">
-        <v>37</v>
+        <v>6323</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1408,15 +1408,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C59">
-        <v>41</v>
+        <v>7660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1426,15 +1426,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C60">
-        <v>45</v>
+        <v>9274</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1444,15 +1444,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C61">
-        <v>56</v>
+        <v>10832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1462,15 +1462,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C62">
-        <v>85</v>
+        <v>11850</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1480,15 +1480,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C63">
-        <v>78</v>
+        <v>14372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1498,15 +1498,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C64">
-        <v>72</v>
+        <v>15605</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1516,15 +1516,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C65">
-        <v>68</v>
+        <v>14870</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1534,15 +1534,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C66">
-        <v>48</v>
+        <v>13532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1552,15 +1552,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C67">
-        <v>63</v>
+        <v>16144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1570,15 +1570,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C68">
-        <v>72</v>
+        <v>15467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1588,15 +1588,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C69">
-        <v>80</v>
+        <v>15239</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1606,15 +1606,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C70">
-        <v>2550</v>
+        <v>1032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1624,15 +1624,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C71">
-        <v>2987</v>
+        <v>728</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1642,15 +1642,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C72">
-        <v>3234</v>
+        <v>704</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1660,15 +1660,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C73">
-        <v>3630</v>
+        <v>899</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1678,15 +1678,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C74">
-        <v>5151</v>
+        <v>1122</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1696,15 +1696,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C75">
-        <v>6323</v>
+        <v>1240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1714,15 +1714,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C76">
-        <v>7660</v>
+        <v>1539</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1732,15 +1732,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C77">
-        <v>9274</v>
+        <v>1547</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1750,15 +1750,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C78">
-        <v>10832</v>
+        <v>2048</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1768,15 +1768,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C79">
-        <v>11850</v>
+        <v>1978</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1786,15 +1786,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C80">
-        <v>14372</v>
+        <v>2161</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1804,15 +1804,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C81">
-        <v>15605</v>
+        <v>2433</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1822,15 +1822,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C82">
-        <v>14870</v>
+        <v>2182</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1840,15 +1840,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C83">
-        <v>13532</v>
+        <v>2169</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1858,15 +1858,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C84">
-        <v>16144</v>
+        <v>2386</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1876,15 +1876,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C85">
-        <v>15467</v>
+        <v>2225</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1894,15 +1894,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C86">
-        <v>15239</v>
+        <v>1553</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1912,15 +1912,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C87">
-        <v>495</v>
+        <v>1269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1930,15 +1930,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C88">
-        <v>730</v>
+        <v>1229</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1948,15 +1948,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C89">
-        <v>723</v>
+        <v>1364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1966,15 +1966,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C90">
-        <v>758</v>
+        <v>1656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -1984,15 +1984,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C91">
-        <v>1123</v>
+        <v>2113</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2002,15 +2002,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C92">
-        <v>1295</v>
+        <v>2597</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2020,15 +2020,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C93">
-        <v>1461</v>
+        <v>3355</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C94">
-        <v>1696</v>
+        <v>3808</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2056,15 +2056,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C95">
-        <v>1947</v>
+        <v>4849</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C96">
-        <v>2155</v>
+        <v>5282</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2092,15 +2092,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C97">
-        <v>2366</v>
+        <v>6301</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2110,15 +2110,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C98">
-        <v>2418</v>
+        <v>6248</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2128,15 +2128,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C99">
-        <v>2339</v>
+        <v>6037</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2146,15 +2146,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C100">
-        <v>2021</v>
+        <v>5212</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2164,15 +2164,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C101">
-        <v>2344</v>
+        <v>6156</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C102">
-        <v>2275</v>
+        <v>6386</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2200,15 +2200,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C103">
-        <v>2206</v>
+        <v>6137</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C104">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C105">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C106">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C107">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C108">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C109">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C110">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C111">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C112">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C113">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C114">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C115">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C116">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C117">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C118">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C119">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Amarela</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="C120">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2524,15 +2524,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C121">
-        <v>1695</v>
+        <v>657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2542,15 +2542,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C122">
-        <v>2166</v>
+        <v>829</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2560,15 +2560,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C123">
-        <v>2402</v>
+        <v>1043</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2578,15 +2578,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C124">
-        <v>2883</v>
+        <v>1180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2596,15 +2596,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C125">
-        <v>3848</v>
+        <v>1763</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C126">
-        <v>4650</v>
+        <v>2034</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2632,15 +2632,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C127">
-        <v>6118</v>
+        <v>2474</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2650,15 +2650,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C128">
-        <v>7867</v>
+        <v>3270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2668,15 +2668,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C129">
-        <v>9904</v>
+        <v>3950</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2686,15 +2686,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C130">
-        <v>11734</v>
+        <v>4734</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2704,15 +2704,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C131">
-        <v>15100</v>
+        <v>6248</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2722,15 +2722,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C132">
-        <v>18156</v>
+        <v>7720</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2740,15 +2740,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C133">
-        <v>18444</v>
+        <v>7869</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C134">
-        <v>17936</v>
+        <v>8022</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2776,15 +2776,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C135">
-        <v>20413</v>
+        <v>8987</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2794,15 +2794,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C136">
-        <v>23973</v>
+        <v>9767</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2812,15 +2812,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Branca</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C137">
-        <v>25244</v>
+        <v>10947</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2830,15 +2830,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C138">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2848,15 +2848,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C139">
-        <v>761</v>
+        <v>171</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2866,15 +2866,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C140">
-        <v>714</v>
+        <v>173</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2884,15 +2884,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C141">
-        <v>911</v>
+        <v>140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C142">
-        <v>1437</v>
+        <v>156</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2920,15 +2920,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C143">
-        <v>1622</v>
+        <v>130</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2938,15 +2938,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C144">
-        <v>2067</v>
+        <v>133</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2956,15 +2956,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C145">
-        <v>2455</v>
+        <v>144</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2974,15 +2974,15 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C146">
-        <v>2881</v>
+        <v>223</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -2992,15 +2992,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C147">
-        <v>3094</v>
+        <v>234</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3010,15 +3010,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C148">
-        <v>3230</v>
+        <v>269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3028,15 +3028,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C149">
-        <v>4375</v>
+        <v>322</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C150">
-        <v>4515</v>
+        <v>327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3064,15 +3064,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C151">
-        <v>4178</v>
+        <v>295</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3082,15 +3082,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C152">
-        <v>4598</v>
+        <v>304</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3100,15 +3100,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C153">
-        <v>5201</v>
+        <v>325</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3118,15 +3118,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ignorado</t>
+          <t>Indigenous</t>
         </is>
       </c>
       <c r="C154">
-        <v>3695</v>
+        <v>365</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3136,15 +3136,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C155">
-        <v>82</v>
+        <v>2571</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3154,15 +3154,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C156">
-        <v>171</v>
+        <v>3277</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3172,15 +3172,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C157">
-        <v>173</v>
+        <v>3735</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C158">
-        <v>140</v>
+        <v>4522</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3208,15 +3208,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C159">
-        <v>156</v>
+        <v>6265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3226,15 +3226,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C160">
-        <v>130</v>
+        <v>7492</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3244,15 +3244,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C161">
-        <v>133</v>
+        <v>9479</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3262,15 +3262,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C162">
-        <v>144</v>
+        <v>12346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3280,15 +3280,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C163">
-        <v>223</v>
+        <v>15032</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3298,15 +3298,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C164">
-        <v>234</v>
+        <v>17861</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3316,15 +3316,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C165">
-        <v>269</v>
+        <v>23706</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C166">
-        <v>322</v>
+        <v>31977</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3352,15 +3352,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C167">
-        <v>327</v>
+        <v>33279</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3370,15 +3370,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C168">
-        <v>295</v>
+        <v>34277</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3388,15 +3388,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C169">
-        <v>304</v>
+        <v>40032</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3406,15 +3406,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C170">
-        <v>325</v>
+        <v>43515</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3424,15 +3424,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Indígena</t>
+          <t>Mixed-race</t>
         </is>
       </c>
       <c r="C171">
-        <v>365</v>
+        <v>46117</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3442,15 +3442,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C172">
-        <v>2571</v>
+        <v>657</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3460,15 +3460,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C173">
-        <v>3277</v>
+        <v>761</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C174">
-        <v>3735</v>
+        <v>714</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3496,15 +3496,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C175">
-        <v>4522</v>
+        <v>911</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3514,15 +3514,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C176">
-        <v>6265</v>
+        <v>1437</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3532,15 +3532,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C177">
-        <v>7492</v>
+        <v>1622</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3550,15 +3550,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C178">
-        <v>9479</v>
+        <v>2067</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3568,15 +3568,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C179">
-        <v>12346</v>
+        <v>2455</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3586,15 +3586,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C180">
-        <v>15032</v>
+        <v>2881</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3604,15 +3604,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C181">
-        <v>17861</v>
+        <v>3094</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C182">
-        <v>23706</v>
+        <v>3230</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3640,15 +3640,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C183">
-        <v>31977</v>
+        <v>4375</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C184">
-        <v>33279</v>
+        <v>4515</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3676,15 +3676,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C185">
-        <v>34277</v>
+        <v>4178</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3694,15 +3694,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C186">
-        <v>40032</v>
+        <v>4598</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3712,15 +3712,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C187">
-        <v>43515</v>
+        <v>5201</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3730,15 +3730,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Parda</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C188">
-        <v>46117</v>
+        <v>3695</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3748,15 +3748,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C189">
-        <v>657</v>
+        <v>1695</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C190">
-        <v>829</v>
+        <v>2166</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3784,15 +3784,15 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C191">
-        <v>1043</v>
+        <v>2402</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3802,15 +3802,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C192">
-        <v>1180</v>
+        <v>2883</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3820,15 +3820,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C193">
-        <v>1763</v>
+        <v>3848</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3838,15 +3838,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C194">
-        <v>2034</v>
+        <v>4650</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3856,15 +3856,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C195">
-        <v>2474</v>
+        <v>6118</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3874,15 +3874,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C196">
-        <v>3270</v>
+        <v>7867</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3892,15 +3892,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C197">
-        <v>3950</v>
+        <v>9904</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C198">
-        <v>4734</v>
+        <v>11734</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3928,15 +3928,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C199">
-        <v>6248</v>
+        <v>15100</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3946,15 +3946,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C200">
-        <v>7720</v>
+        <v>18156</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3964,15 +3964,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C201">
-        <v>7869</v>
+        <v>18444</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -3982,15 +3982,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C202">
-        <v>8022</v>
+        <v>17936</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -4000,15 +4000,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C203">
-        <v>8987</v>
+        <v>20413</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -4018,15 +4018,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C204">
-        <v>9767</v>
+        <v>23973</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
@@ -4036,15 +4036,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Preta</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C205">
-        <v>10947</v>
+        <v>25244</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
     </row>
